--- a/homework/数据通路表、控制信号取值表_miniRV_控制信号已完成.xlsx
+++ b/homework/数据通路表、控制信号取值表_miniRV_控制信号已完成.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CpuDesign\homework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198634D7-3AEE-42C4-AB37-200439E515B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E855221B-EAD0-4463-A041-08E8322F93FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="20" windowWidth="25480" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数据通路表(含控制信号)" sheetId="1" r:id="rId1"/>
@@ -348,257 +348,257 @@
     <t>bgeu</t>
   </si>
   <si>
+    <t>RF.rD1
+PC.pc</t>
+  </si>
+  <si>
+    <t>ram_wop</t>
+  </si>
+  <si>
+    <t>alua_sel</t>
+  </si>
+  <si>
+    <t>控制信号取值表-示例</t>
+  </si>
+  <si>
+    <t>指令</t>
+  </si>
+  <si>
+    <t>opcode</t>
+  </si>
+  <si>
+    <t>funct3</t>
+  </si>
+  <si>
+    <t>funct7</t>
+  </si>
+  <si>
+    <t>控制信号</t>
+  </si>
+  <si>
+    <t>PC4</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>WB_ALU</t>
+  </si>
+  <si>
+    <t>I_TYPE</t>
+  </si>
+  <si>
+    <t>ADD</t>
+  </si>
+  <si>
+    <t>SEL_EXT</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>SLL</t>
+  </si>
+  <si>
+    <t>WB_EXT</t>
+  </si>
+  <si>
+    <t>U_TYPE</t>
+  </si>
+  <si>
+    <t>WB_RAM</t>
+  </si>
+  <si>
+    <t>WORD_EXT</t>
+  </si>
+  <si>
+    <t>BRANCH</t>
+  </si>
+  <si>
+    <t>B_TYPE</t>
+  </si>
+  <si>
+    <t>EQ</t>
+  </si>
+  <si>
+    <t>SEL_RS2</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>JUMP</t>
+  </si>
+  <si>
+    <t>WB_PC4</t>
+  </si>
+  <si>
+    <t>J_TYPE</t>
+  </si>
+  <si>
+    <t>0010011</t>
+  </si>
+  <si>
+    <t>000</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>0000000</t>
+  </si>
+  <si>
+    <t>0110111</t>
+  </si>
+  <si>
+    <t>0000011</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>1100011</t>
+  </si>
+  <si>
+    <t>1101111</t>
+  </si>
+  <si>
+    <t>0110011</t>
+  </si>
+  <si>
+    <t>SEL_RS1</t>
+  </si>
+  <si>
+    <t>0100000</t>
+  </si>
+  <si>
+    <t>SUB</t>
+  </si>
+  <si>
+    <t>0010111</t>
+  </si>
+  <si>
+    <t>SEL_PC</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>SRL</t>
+  </si>
+  <si>
+    <t>SRA</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>XOR</t>
+  </si>
+  <si>
+    <t>BYTE_EXT</t>
+  </si>
+  <si>
+    <t>BYTE_UEXT</t>
+  </si>
+  <si>
+    <t>HALF_EXT</t>
+  </si>
+  <si>
+    <t>HALF_UEXT</t>
+  </si>
+  <si>
+    <t>0100011</t>
+  </si>
+  <si>
+    <t>S_TYPE</t>
+  </si>
+  <si>
+    <t>WORD_WE</t>
+  </si>
+  <si>
+    <t>BYTE_WE</t>
+  </si>
+  <si>
+    <t>HALF_WE</t>
+  </si>
+  <si>
+    <t>1100111</t>
+  </si>
+  <si>
+    <t>0000001</t>
+  </si>
+  <si>
+    <t>MUL</t>
+  </si>
+  <si>
+    <t>MULH</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>MULHU</t>
+  </si>
+  <si>
+    <t>DIV</t>
+  </si>
+  <si>
+    <t>DIVU</t>
+  </si>
+  <si>
+    <t>REM</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>REMU</t>
+  </si>
+  <si>
+    <t>SLT</t>
+  </si>
+  <si>
+    <t>SLTU</t>
+  </si>
+  <si>
+    <t>AND</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>LTU</t>
+  </si>
+  <si>
+    <t>GEU</t>
+  </si>
+  <si>
+    <t>is_mul</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_div</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>ALU.C
+SEXT.ext
 MEXT.ext
 NPC.pc4</t>
-  </si>
-  <si>
-    <t>RF.rD1
-PC.pc</t>
-  </si>
-  <si>
-    <t>ram_wop</t>
-  </si>
-  <si>
-    <t>alua_sel</t>
-  </si>
-  <si>
-    <t>控制信号取值表-示例</t>
-  </si>
-  <si>
-    <t>指令</t>
-  </si>
-  <si>
-    <t>opcode</t>
-  </si>
-  <si>
-    <t>funct3</t>
-  </si>
-  <si>
-    <t>funct7</t>
-  </si>
-  <si>
-    <t>控制信号</t>
-  </si>
-  <si>
-    <t>PC4</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>WB_ALU</t>
-  </si>
-  <si>
-    <t>I_TYPE</t>
-  </si>
-  <si>
-    <t>ADD</t>
-  </si>
-  <si>
-    <t>SEL_EXT</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>SLL</t>
-  </si>
-  <si>
-    <t>WB_EXT</t>
-  </si>
-  <si>
-    <t>U_TYPE</t>
-  </si>
-  <si>
-    <t>WB_RAM</t>
-  </si>
-  <si>
-    <t>WORD_EXT</t>
-  </si>
-  <si>
-    <t>BRANCH</t>
-  </si>
-  <si>
-    <t>B_TYPE</t>
-  </si>
-  <si>
-    <t>EQ</t>
-  </si>
-  <si>
-    <t>SEL_RS2</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>JUMP</t>
-  </si>
-  <si>
-    <t>WB_PC4</t>
-  </si>
-  <si>
-    <t>J_TYPE</t>
-  </si>
-  <si>
-    <t>0010011</t>
-  </si>
-  <si>
-    <t>000</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>0000000</t>
-  </si>
-  <si>
-    <t>0110111</t>
-  </si>
-  <si>
-    <t>0000011</t>
-  </si>
-  <si>
-    <t>010</t>
-  </si>
-  <si>
-    <t>1100011</t>
-  </si>
-  <si>
-    <t>1101111</t>
-  </si>
-  <si>
-    <t>0110011</t>
-  </si>
-  <si>
-    <t>SEL_RS1</t>
-  </si>
-  <si>
-    <t>0100000</t>
-  </si>
-  <si>
-    <t>SUB</t>
-  </si>
-  <si>
-    <t>0010111</t>
-  </si>
-  <si>
-    <t>SEL_PC</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>SRL</t>
-  </si>
-  <si>
-    <t>SRA</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>XOR</t>
-  </si>
-  <si>
-    <t>BYTE_EXT</t>
-  </si>
-  <si>
-    <t>BYTE_UEXT</t>
-  </si>
-  <si>
-    <t>HALF_EXT</t>
-  </si>
-  <si>
-    <t>HALF_UEXT</t>
-  </si>
-  <si>
-    <t>0100011</t>
-  </si>
-  <si>
-    <t>S_TYPE</t>
-  </si>
-  <si>
-    <t>WORD_WE</t>
-  </si>
-  <si>
-    <t>BYTE_WE</t>
-  </si>
-  <si>
-    <t>HALF_WE</t>
-  </si>
-  <si>
-    <t>1100111</t>
-  </si>
-  <si>
-    <t>0000001</t>
-  </si>
-  <si>
-    <t>MUL</t>
-  </si>
-  <si>
-    <t>MULH</t>
-  </si>
-  <si>
-    <t>011</t>
-  </si>
-  <si>
-    <t>MULHU</t>
-  </si>
-  <si>
-    <t>DIV</t>
-  </si>
-  <si>
-    <t>DIVU</t>
-  </si>
-  <si>
-    <t>REM</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>REMU</t>
-  </si>
-  <si>
-    <t>SLT</t>
-  </si>
-  <si>
-    <t>SLTU</t>
-  </si>
-  <si>
-    <t>AND</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>GE</t>
-  </si>
-  <si>
-    <t>LTU</t>
-  </si>
-  <si>
-    <t>GEU</t>
-  </si>
-  <si>
-    <t>is_mul</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>is_div</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>alu_op
-is_mul
-is_div</t>
+    <t>alu_op</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -819,7 +819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -910,37 +910,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -964,6 +952,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -982,13 +991,7 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1225,50 +1228,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B2" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
+      <c r="B2" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="35" t="s">
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="35" t="s">
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="37"/>
-      <c r="N3" s="30" t="s">
+      <c r="M3" s="49"/>
+      <c r="N3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B4" s="9" t="s">
@@ -1277,32 +1280,32 @@
       <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="31" t="s">
+      <c r="E4" s="50"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="32"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="36"/>
       <c r="K4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="L4" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="32"/>
-      <c r="N4" s="31" t="s">
+      <c r="M4" s="36"/>
+      <c r="N4" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="32"/>
-      <c r="P4" s="31" t="s">
+      <c r="O4" s="36"/>
+      <c r="P4" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="32"/>
+      <c r="Q4" s="36"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B5" s="9" t="s">
@@ -1811,36 +1814,36 @@
       <c r="C15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="32"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="36"/>
       <c r="G15" s="5" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="31" t="s">
+      <c r="I15" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J15" s="32"/>
+      <c r="J15" s="36"/>
       <c r="K15" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L15" s="31" t="s">
+      <c r="L15" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="M15" s="32"/>
-      <c r="N15" s="31" t="s">
+      <c r="M15" s="36"/>
+      <c r="N15" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="O15" s="32"/>
-      <c r="P15" s="31" t="s">
+      <c r="O15" s="36"/>
+      <c r="P15" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="Q15" s="32"/>
+      <c r="Q15" s="36"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B16" s="11" t="s">
@@ -1896,29 +1899,29 @@
       <c r="B19" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="44" t="s">
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="44" t="s">
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="M19" s="46"/>
-      <c r="N19" s="47" t="s">
+      <c r="M19" s="42"/>
+      <c r="N19" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" s="7" t="s">
@@ -1927,32 +1930,32 @@
       <c r="C20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="43"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="41" t="s">
+      <c r="E20" s="39"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="42"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="38"/>
       <c r="K20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="41" t="s">
+      <c r="L20" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="M20" s="42"/>
-      <c r="N20" s="41" t="s">
+      <c r="M20" s="38"/>
+      <c r="N20" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="O20" s="42"/>
-      <c r="P20" s="41" t="s">
+      <c r="O20" s="38"/>
+      <c r="P20" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="Q20" s="42"/>
+      <c r="Q20" s="38"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B21" s="7" t="s">
@@ -3829,14 +3832,14 @@
       <c r="I58" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="J58" s="20" t="s">
-        <v>107</v>
+      <c r="J58" s="57" t="s">
+        <v>187</v>
       </c>
       <c r="K58" s="20" t="s">
         <v>59</v>
       </c>
       <c r="L58" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M58" s="21" t="s">
         <v>60</v>
@@ -3858,32 +3861,32 @@
       <c r="B59" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D59" s="39" t="s">
+      <c r="D59" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="I59" s="39" t="s">
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="I59" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="J59" s="39"/>
+      <c r="J59" s="32"/>
       <c r="K59" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="L59" s="56" t="s">
+      <c r="L59" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="M59" s="39"/>
+      <c r="M59" s="32"/>
       <c r="N59" s="18" t="s">
         <v>66</v>
       </c>
       <c r="O59" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="P59" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="P59" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="Q59" s="39"/>
+      <c r="Q59" s="32"/>
     </row>
     <row r="60" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B60" s="10" t="s">
@@ -3893,7 +3896,7 @@
         <v>68</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>69</v>
@@ -3901,6 +3904,19 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="D15:F15"/>
     <mergeCell ref="D59:F59"/>
     <mergeCell ref="I59:J59"/>
     <mergeCell ref="L59:M59"/>
@@ -3916,19 +3932,6 @@
     <mergeCell ref="L20:M20"/>
     <mergeCell ref="N19:Q19"/>
     <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="D15:F15"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3956,16 +3959,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B2" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
+      <c r="B2" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -3974,36 +3977,36 @@
       <c r="O2" s="12"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="D3" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="E3" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="F3" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
       <c r="M3"/>
       <c r="N3"/>
       <c r="O3"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B4" s="51"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
       <c r="F4" s="8" t="s">
         <v>62</v>
       </c>
@@ -4025,11 +4028,11 @@
       <c r="L4" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="M4" s="54" t="s">
+      <c r="M4" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="N4" s="30" t="s">
         <v>186</v>
-      </c>
-      <c r="N4" s="54" t="s">
-        <v>187</v>
       </c>
       <c r="O4"/>
     </row>
@@ -4038,34 +4041,34 @@
         <v>30</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>139</v>
-      </c>
       <c r="E5" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>122</v>
-      </c>
       <c r="L5" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -4080,34 +4083,34 @@
         <v>40</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>120</v>
-      </c>
       <c r="J6" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -4122,34 +4125,34 @@
         <v>41</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="E7" s="22" t="s">
-        <v>142</v>
-      </c>
       <c r="F7" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>120</v>
-      </c>
       <c r="J7" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -4164,7 +4167,7 @@
         <v>42</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>33</v>
@@ -4173,17 +4176,17 @@
         <v>33</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>118</v>
-      </c>
       <c r="H8" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="J8" s="8" t="s">
         <v>33</v>
       </c>
@@ -4191,7 +4194,7 @@
         <v>33</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -4206,34 +4209,34 @@
         <v>44</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>145</v>
-      </c>
       <c r="E9" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>118</v>
-      </c>
       <c r="H9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>128</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>129</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -4248,34 +4251,34 @@
         <v>48</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="8" t="s">
+      <c r="J10" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>133</v>
-      </c>
       <c r="L10" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -4290,34 +4293,34 @@
         <v>53</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E11" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>131</v>
-      </c>
       <c r="J11" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -4332,7 +4335,7 @@
         <v>54</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>33</v>
@@ -4341,17 +4344,17 @@
         <v>33</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G12" s="5">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>137</v>
-      </c>
       <c r="J12" s="8" t="s">
         <v>33</v>
       </c>
@@ -4359,7 +4362,7 @@
         <v>33</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -4370,36 +4373,36 @@
       <c r="O12"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="D15" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="E15" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="F15" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
       <c r="O15"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B16" s="48"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
       <c r="F16" s="4" t="s">
         <v>62</v>
       </c>
@@ -4416,7 +4419,7 @@
         <v>65</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>69</v>
@@ -4425,13 +4428,13 @@
         <v>66</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="O16" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="O16" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="P16" s="31" t="s">
         <v>186</v>
-      </c>
-      <c r="P16" s="55" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.35">
@@ -4439,40 +4442,40 @@
         <v>70</v>
       </c>
       <c r="C17" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L17" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -4486,40 +4489,40 @@
         <v>71</v>
       </c>
       <c r="C18" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L18" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -4533,40 +4536,40 @@
         <v>72</v>
       </c>
       <c r="C19" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D19" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="J19" s="4" t="s">
+      <c r="L19" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M19" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4580,40 +4583,40 @@
         <v>73</v>
       </c>
       <c r="C20" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L20" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -4627,40 +4630,40 @@
         <v>74</v>
       </c>
       <c r="C21" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L21" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -4674,40 +4677,40 @@
         <v>75</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D22" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E22" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="K22" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4721,40 +4724,40 @@
         <v>76</v>
       </c>
       <c r="C23" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="L23" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4768,40 +4771,40 @@
         <v>77</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="J24" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -4815,40 +4818,40 @@
         <v>78</v>
       </c>
       <c r="C25" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="E25" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L25" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -4862,40 +4865,40 @@
         <v>79</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D26" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E26" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="K26" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4909,40 +4912,40 @@
         <v>80</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E27" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F27" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="H27" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="K27" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M27" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4956,40 +4959,40 @@
         <v>81</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E28" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="H28" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M28" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -5003,40 +5006,40 @@
         <v>82</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E29" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="H29" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="K29" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M29" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -5050,40 +5053,40 @@
         <v>83</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E30" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="H30" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="K30" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M30" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -5097,40 +5100,40 @@
         <v>84</v>
       </c>
       <c r="C31" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D31" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I31" s="1" t="s">
+      <c r="J31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5144,40 +5147,40 @@
         <v>86</v>
       </c>
       <c r="C32" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D32" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="J32" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5191,40 +5194,40 @@
         <v>87</v>
       </c>
       <c r="C33" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D33" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="J33" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5238,40 +5241,40 @@
         <v>88</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E34" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="I34" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="K34" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -5285,40 +5288,40 @@
         <v>89</v>
       </c>
       <c r="C35" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L35" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O35">
         <v>1</v>
@@ -5332,40 +5335,40 @@
         <v>90</v>
       </c>
       <c r="C36" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D36" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L36" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O36">
         <v>1</v>
@@ -5379,40 +5382,40 @@
         <v>91</v>
       </c>
       <c r="C37" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D37" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L37" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O37">
         <v>1</v>
@@ -5426,40 +5429,40 @@
         <v>92</v>
       </c>
       <c r="C38" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D38" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L38" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5473,40 +5476,40 @@
         <v>93</v>
       </c>
       <c r="C39" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D39" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L39" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -5520,40 +5523,40 @@
         <v>94</v>
       </c>
       <c r="C40" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D40" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="L40" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5567,40 +5570,40 @@
         <v>95</v>
       </c>
       <c r="C41" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H41" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="J41" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="K41" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="D41" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="E41" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="H41" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="I41" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J41" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="K41" s="26" t="s">
-        <v>149</v>
-      </c>
       <c r="L41" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M41" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N41" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -5614,40 +5617,40 @@
         <v>96</v>
       </c>
       <c r="C42" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H42" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="J42" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="K42" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="D42" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="F42" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="H42" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="I42" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J42" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="K42" s="26" t="s">
-        <v>149</v>
-      </c>
       <c r="L42" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N42" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -5661,40 +5664,40 @@
         <v>97</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E43" s="27" t="s">
         <v>33</v>
       </c>
       <c r="F43" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G43" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="G43" s="26" t="s">
+      <c r="H43" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="H43" s="26" t="s">
+      <c r="I43" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="I43" s="26" t="s">
-        <v>120</v>
-      </c>
       <c r="J43" s="26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K43" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L43" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M43" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N43" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -5708,40 +5711,40 @@
         <v>98</v>
       </c>
       <c r="C44" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G44" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H44" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I44" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="J44" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="K44" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="D44" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="E44" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="F44" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="G44" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="I44" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J44" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="K44" s="26" t="s">
-        <v>149</v>
-      </c>
       <c r="L44" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N44" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -5755,40 +5758,40 @@
         <v>99</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E45" s="27" t="s">
         <v>33</v>
       </c>
       <c r="F45" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G45" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="G45" s="26" t="s">
+      <c r="H45" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="H45" s="26" t="s">
+      <c r="I45" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="I45" s="26" t="s">
-        <v>120</v>
-      </c>
       <c r="J45" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K45" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L45" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M45" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N45" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -5802,40 +5805,40 @@
         <v>100</v>
       </c>
       <c r="C46" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H46" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I46" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="J46" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="K46" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="D46" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E46" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="F46" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="G46" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="H46" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="I46" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J46" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="K46" s="26" t="s">
-        <v>149</v>
-      </c>
       <c r="L46" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M46" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N46" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -5849,40 +5852,40 @@
         <v>101</v>
       </c>
       <c r="C47" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="H47" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="I47" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="K47" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="D47" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="E47" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="F47" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="G47" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="H47" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="I47" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J47" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="K47" s="26" t="s">
-        <v>149</v>
-      </c>
       <c r="L47" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N47" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -5896,40 +5899,40 @@
         <v>102</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E48" s="27" t="s">
         <v>33</v>
       </c>
       <c r="F48" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="G48" s="26" t="s">
+      <c r="H48" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="H48" s="26" t="s">
+      <c r="I48" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="I48" s="26" t="s">
-        <v>120</v>
-      </c>
       <c r="J48" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K48" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L48" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M48" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N48" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -5943,40 +5946,40 @@
         <v>103</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E49" s="27" t="s">
         <v>33</v>
       </c>
       <c r="F49" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="H49" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="G49" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="H49" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="I49" s="26" t="s">
-        <v>131</v>
-      </c>
       <c r="J49" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K49" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L49" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M49" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N49" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -5990,40 +5993,40 @@
         <v>104</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E50" s="27" t="s">
         <v>33</v>
       </c>
       <c r="F50" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="H50" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I50" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="G50" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="H50" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="I50" s="26" t="s">
-        <v>131</v>
-      </c>
       <c r="J50" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K50" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L50" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M50" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N50" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -6037,40 +6040,40 @@
         <v>105</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E51" s="27" t="s">
         <v>33</v>
       </c>
       <c r="F51" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="H51" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I51" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="G51" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="H51" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="I51" s="26" t="s">
-        <v>131</v>
-      </c>
       <c r="J51" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K51" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L51" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M51" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N51" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -6084,40 +6087,40 @@
         <v>106</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E52" s="27" t="s">
         <v>33</v>
       </c>
       <c r="F52" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="G52" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="H52" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I52" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="G52" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="H52" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="I52" s="26" t="s">
-        <v>131</v>
-      </c>
       <c r="J52" s="26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K52" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L52" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M52" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N52" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O52">
         <v>0</v>
